--- a/data/papers/secondary_paper.xlsx
+++ b/data/papers/secondary_paper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pancho/Library/CloudStorage/GoogleDrive-amizuno@ualberta.ca/My Drive/systematic_mapping_AnimCogn/data/papers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F41809-D465-DC44-9F0A-7ABF94CE4691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A96D345-1F0E-9A4F-A5B3-56740467CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7020" yWindow="760" windowWidth="21360" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="21360" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="1" r:id="rId1"/>
@@ -1757,7 +1757,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1775,19 +1775,27 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow (Body)"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow (Body)"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1811,19 +1819,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2043,1172 +2052,1225 @@
   <dimension ref="A1:AA998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.6640625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="27" width="10.83203125" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="11.1640625" style="2"/>
+    <col min="1" max="1" width="53.6640625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="10.83203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.5" style="5" customWidth="1"/>
+    <col min="7" max="27" width="10.83203125" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="11.1640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="6">
         <v>2023</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="6">
         <v>2017</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="6">
         <v>2005</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="6">
         <v>2016</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="6" t="s">
         <v>31</v>
       </c>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="6">
         <v>2023</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="6">
         <v>2016</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="6">
         <v>2021</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="6" t="s">
         <v>49</v>
       </c>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="6">
         <v>2021</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
         <v>54</v>
       </c>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="6">
         <v>2022</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="6">
         <v>2020</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="6" t="s">
         <v>66</v>
       </c>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="6">
         <v>2018</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="6" t="s">
         <v>72</v>
       </c>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="6">
         <v>2024</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="6" t="s">
         <v>77</v>
       </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="6">
         <v>2018</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="6" t="s">
         <v>83</v>
       </c>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="6">
         <v>2022</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="6" t="s">
         <v>89</v>
       </c>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="6">
         <v>2024</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="6">
         <v>2008</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="6" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="6">
         <v>2021</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="6">
         <v>2022</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="6">
         <v>2018</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="6">
         <v>2021</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="6">
         <v>2019</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="6" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="6">
         <v>2019</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="6" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="6">
         <v>2022</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="6" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="6">
         <v>2016</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="6" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="6">
         <v>2019</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="6" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="6">
         <v>2023</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="6" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="6">
         <v>2005</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="6" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="6">
         <v>2020</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="6">
         <v>2018</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="6">
         <v>2019</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="6" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="6">
         <v>2019</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="6" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="6">
         <v>2012</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="6">
         <v>2024</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="6" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="6">
         <v>2022</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="6" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="6">
         <v>2014</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="6" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="6">
         <v>2019</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="6" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="6">
         <v>2019</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="6" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="6">
         <v>2024</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="6" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="6">
         <v>2017</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="6" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="6">
         <v>2020</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="6" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="6">
         <v>2019</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="6" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="6">
         <v>2015</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="6" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="6">
         <v>2018</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="6" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="6">
         <v>2020</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="6" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="6">
         <v>2021</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="6" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="6">
         <v>2022</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="6" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="6">
         <v>2024</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="6" t="s">
         <v>271</v>
       </c>
+      <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="6">
         <v>2020</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="6" t="s">
         <v>276</v>
       </c>
+      <c r="H49" s="6"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="6">
         <v>2022</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="E50" s="6"/>
+      <c r="F50" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6" t="s">
         <v>281</v>
       </c>
     </row>
@@ -3226,940 +3288,940 @@
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4171,1311 +4233,1311 @@
   <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="1">
         <v>2001</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>2008</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="1">
         <v>2015</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>2013</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>2021</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="1">
         <v>2013</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>2019</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>2013</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="1">
         <v>2017</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>2013</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="1" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="1">
         <v>2024</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="1" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>2017</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="1" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="1">
         <v>2006</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="1">
         <v>2007</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="1">
         <v>2017</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>2009</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="1" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>2022</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="1" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="1">
         <v>2014</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="1" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="1">
         <v>2012</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="1" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="1">
         <v>2023</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="1" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="1">
         <v>2021</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="1" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="1">
         <v>2020</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="1" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="1">
         <v>2014</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="1" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="1">
         <v>2024</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="1" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="1">
         <v>2019</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="1" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="1">
         <v>2019</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="1" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="1">
         <v>2004</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="1" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="1">
         <v>2023</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="1" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="1">
         <v>1996</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="1" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="1">
         <v>2013</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="1" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>2004</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="1" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="1">
         <v>2023</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="1" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="1">
         <v>2022</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="1" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>2015</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="1" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="1">
         <v>2016</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="1" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="1">
         <v>2003</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="1" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="1">
         <v>2023</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="1" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="1">
         <v>2020</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="1" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="1">
         <v>2019</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="1" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="1">
         <v>2013</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="1" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="1">
         <v>2024</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="1" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="1">
         <v>2015</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="1" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="1">
         <v>2024</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="1" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="1">
         <v>2022</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="1" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="1">
         <v>2020</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="1" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="1">
         <v>2020</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="1" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="1">
         <v>2014</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="1" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="1">
         <v>2016</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="1" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="1">
         <v>2002</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="1" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="1">
         <v>2003</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="1" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="1">
         <v>2002</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="1" t="s">
         <v>572</v>
       </c>
     </row>
